--- a/ci-build/ValueSet-vs-senologie-zweittumor.xlsx
+++ b/ci-build/ValueSet-vs-senologie-zweittumor.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T14:42:03+00:00</t>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +125,30 @@
   </si>
   <si>
     <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -313,66 +341,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -391,50 +421,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B6" t="s" s="2">
-        <v>35</v>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
